--- a/design_tables/excel/Card.xlsx
+++ b/design_tables/excel/Card.xlsx
@@ -573,8 +573,10 @@
       <c r="D4" t="n">
         <v>0</v>
       </c>
-      <c r="E4" t="n">
-        <v>20</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>transform</t>
+        </is>
       </c>
       <c r="F4" t="n">
         <v>10</v>
@@ -612,7 +614,6 @@
           <t>res://assets/ui/card_frame_player.png</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5" ht="25.5" customHeight="1">
       <c r="A5" t="inlineStr">
@@ -633,8 +634,10 @@
       <c r="D5" t="n">
         <v>1</v>
       </c>
-      <c r="E5" t="n">
-        <v>10</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
       </c>
       <c r="F5" t="n">
         <v>20</v>
@@ -672,7 +675,6 @@
           <t>res://assets/ui/card_frame_player.png</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6" ht="25.5" customHeight="1">
       <c r="A6" t="inlineStr">
@@ -693,8 +695,10 @@
       <c r="D6" t="n">
         <v>1</v>
       </c>
-      <c r="E6" t="n">
-        <v>10</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>skill</t>
+        </is>
       </c>
       <c r="F6" t="n">
         <v>10</v>
@@ -732,7 +736,6 @@
           <t>res://assets/ui/card_frame_player.png</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7" ht="25.5" customHeight="1">
       <c r="A7" t="inlineStr">
@@ -753,8 +756,10 @@
       <c r="D7" t="n">
         <v>1</v>
       </c>
-      <c r="E7" t="n">
-        <v>10</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>skill</t>
+        </is>
       </c>
       <c r="F7" t="n">
         <v>10</v>
@@ -802,8 +807,10 @@
       <c r="D8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="n">
-        <v>10</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
       </c>
       <c r="F8" t="n">
         <v>30</v>
@@ -841,7 +848,6 @@
           <t>res://assets/ui/card_frame_player.png</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -862,8 +868,10 @@
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="n">
-        <v>40</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>skill</t>
+        </is>
       </c>
       <c r="F9" t="n">
         <v>10</v>
@@ -901,7 +909,6 @@
           <t>res://assets/ui/card_frame_player.png</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -922,8 +929,10 @@
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="n">
-        <v>40</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>skill</t>
+        </is>
       </c>
       <c r="F10" t="n">
         <v>30</v>
@@ -961,7 +970,6 @@
           <t>res://assets/ui/card_frame_player.png</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/design_tables/excel/Card.xlsx
+++ b/design_tables/excel/Card.xlsx
@@ -152,24 +152,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CardTable" displayName="CardTable" ref="A1:J7" headerRowCount="1">
-  <tableColumns count="10">
-    <tableColumn id="1" name="id"/>
-    <tableColumn id="2" name="name"/>
-    <tableColumn id="3" name="cost"/>
-    <tableColumn id="4" name="card_type"/>
-    <tableColumn id="5" name="target"/>
-    <tableColumn id="6" name="play_destination"/>
-    <tableColumn id="7" name="exhaust"/>
-    <tableColumn id="8" name="effect_ids"/>
-    <tableColumn id="9" name="description"/>
-    <tableColumn id="10" name="comment"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -579,7 +561,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>30</v>
@@ -640,7 +622,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
         <v>20</v>
@@ -701,7 +683,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v>20</v>
@@ -762,7 +744,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
         <v>20</v>
@@ -813,7 +795,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
         <v>20</v>
@@ -874,7 +856,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
         <v>20</v>
@@ -935,7 +917,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
         <v>20</v>
@@ -973,8 +955,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>